--- a/sample update purchase app.xlsx
+++ b/sample update purchase app.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dataanalyst\Purchase App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5FA3452-75E7-49B3-B927-A1675ED879AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018A4F91-708F-4694-A73C-7E2726B504FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{482F46A9-C16E-43A2-8FD8-0304FE737902}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,17 +48,17 @@
     <t>Rate</t>
   </si>
   <si>
-    <t>IT001</t>
+    <t>1059-3</t>
   </si>
   <si>
-    <t>IT002</t>
+    <t>BRASS Y STRAINER 3 PN16 PEG IMP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,16 +74,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,17 +111,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -433,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D95602E-BD01-4D30-9B92-5FEE97D09DFE}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -453,28 +501,369 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
+      <c r="A2">
+        <v>300189</v>
       </c>
       <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>45.742399999999996</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3">
+        <v>251340</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" s="3">
-        <v>36</v>
+      <c r="C3">
+        <v>22.7424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>300195</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>158.26760000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>300196</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>192.69399999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>300198</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>405.73839999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>300220</v>
+      </c>
+      <c r="B7">
+        <v>190</v>
+      </c>
+      <c r="C7">
+        <v>9.66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>300226</v>
+      </c>
+      <c r="B8">
+        <v>10000</v>
+      </c>
+      <c r="C8">
+        <v>7.4428000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>300462</v>
+      </c>
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="C9">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>300347</v>
+      </c>
+      <c r="B10">
+        <v>1000</v>
+      </c>
+      <c r="C10">
+        <v>10.6168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>300340</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>20.442399999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>300341</v>
+      </c>
+      <c r="B12">
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <v>23.570399999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>300343</v>
+      </c>
+      <c r="B13">
+        <v>500</v>
+      </c>
+      <c r="C13">
+        <v>84.198399999999992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>300344</v>
+      </c>
+      <c r="B14">
+        <v>200</v>
+      </c>
+      <c r="C14">
+        <v>151.96559999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>300345</v>
+      </c>
+      <c r="B15">
+        <v>500</v>
+      </c>
+      <c r="C15">
+        <v>179.43680000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>300346</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>416.36439999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>300510</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>59.661999999999992</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>263281</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>156.43680000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>300240</v>
+      </c>
+      <c r="B19">
+        <v>4000</v>
+      </c>
+      <c r="C19">
+        <v>7.1943999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>251349</v>
+      </c>
+      <c r="B20">
+        <v>6000</v>
+      </c>
+      <c r="C20">
+        <v>10.009600000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>251350</v>
+      </c>
+      <c r="B21">
+        <v>2000</v>
+      </c>
+      <c r="C21">
+        <v>33.773200000000003</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B171D8-25F4-416B-A3E7-ED957F8D7760}">
+  <dimension ref="A3:C22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="50.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>300189</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>251340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>300195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>300196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>300198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>300220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>300226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>300462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>300347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>300340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>300341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>300343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>300344</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>300345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>300346</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>300510</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>263281</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>300240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>251349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9">
+        <v>251350</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="https://stock.junaidworld.com/item/DIP/300189" xr:uid="{728FB4C0-53B9-4391-B86F-F157B2B8C3A9}"/>
+    <hyperlink ref="A4" r:id="rId2" display="https://stock.junaidworld.com/item/DIP/251340" xr:uid="{19B260F4-16AA-4853-A5A7-3E932C3FBE93}"/>
+    <hyperlink ref="A5" r:id="rId3" display="https://stock.junaidworld.com/item/DIP/300195" xr:uid="{6F3394E5-CBD3-4FB4-802C-D4E96642323C}"/>
+    <hyperlink ref="A6" r:id="rId4" display="https://stock.junaidworld.com/item/DIP/300196" xr:uid="{9E72BB0F-1F47-4BB6-9324-73FABC7703A7}"/>
+    <hyperlink ref="A7" r:id="rId5" display="https://stock.junaidworld.com/item/DIP/300198" xr:uid="{99016A9B-BE5A-4FB8-A8E2-2B057650F656}"/>
+    <hyperlink ref="A8" r:id="rId6" display="https://stock.junaidworld.com/item/DIP/300220" xr:uid="{D30FFD79-B53C-4280-B139-610B5C810919}"/>
+    <hyperlink ref="A9" r:id="rId7" display="https://stock.junaidworld.com/item/DIP/300226" xr:uid="{0C704B6D-12C0-499C-BE32-D450D33EE23F}"/>
+    <hyperlink ref="A10" r:id="rId8" display="https://stock.junaidworld.com/item/DIP/300462" xr:uid="{CA215E7C-C5DC-475B-AAFD-8B6C44949C14}"/>
+    <hyperlink ref="A11" r:id="rId9" display="https://stock.junaidworld.com/item/DIP/300347" xr:uid="{251453D7-0DB6-4B78-B712-8EF3533F0E23}"/>
+    <hyperlink ref="A12" r:id="rId10" display="https://stock.junaidworld.com/item/DIP/300340" xr:uid="{A3601EAF-7FBF-4516-AF31-D94D4610D2FA}"/>
+    <hyperlink ref="A13" r:id="rId11" display="https://stock.junaidworld.com/item/DIP/300341" xr:uid="{F63158BB-6B2D-4F0C-ACCD-39B93662F589}"/>
+    <hyperlink ref="A14" r:id="rId12" display="https://stock.junaidworld.com/item/DIP/300343" xr:uid="{6EEEF43C-2783-4085-8A28-590D4E14D982}"/>
+    <hyperlink ref="A15" r:id="rId13" display="https://stock.junaidworld.com/item/DIP/300344" xr:uid="{132D3B9B-5F24-49A0-B254-04C15D7D1AD1}"/>
+    <hyperlink ref="A16" r:id="rId14" display="https://stock.junaidworld.com/item/DIP/300345" xr:uid="{42D68E3E-FB45-4465-8D12-7C22650D51DA}"/>
+    <hyperlink ref="A17" r:id="rId15" display="https://stock.junaidworld.com/item/DIP/300346" xr:uid="{940B8E6F-0517-47AF-87FB-F151948A68D9}"/>
+    <hyperlink ref="A18" r:id="rId16" display="https://stock.junaidworld.com/item/DIP/300510" xr:uid="{DEF6890C-3F85-4E28-9425-97AFA08B9357}"/>
+    <hyperlink ref="A19" r:id="rId17" display="https://stock.junaidworld.com/item/DIP/263281" xr:uid="{04F10F3A-FCA9-4BB0-BB34-EADA0A0EA9C5}"/>
+    <hyperlink ref="A20" r:id="rId18" display="https://stock.junaidworld.com/item/DIP/300240" xr:uid="{49E6E68F-3CD1-4A40-9BB7-D770B008B78D}"/>
+    <hyperlink ref="A21" r:id="rId19" display="https://stock.junaidworld.com/item/DIP/251349" xr:uid="{6436C553-9427-4683-B609-1552530026F1}"/>
+    <hyperlink ref="A22" r:id="rId20" display="https://stock.junaidworld.com/item/DIP/251350" xr:uid="{99247120-5783-41CC-AFD1-ABF62094916E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>